--- a/Sorteo_Empleados_5.xlsx
+++ b/Sorteo_Empleados_5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sm68099\PYTHON\Bolillero_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8966444-341B-46AC-8D8E-DB53EAC40BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{381042C0-F6B5-4783-8C5B-B7E09FA59BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7B455F77-704B-4AAD-B4EC-346F0192F815}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="57">
   <si>
     <t xml:space="preserve">Nombre </t>
   </si>
@@ -204,6 +204,9 @@
   </si>
   <si>
     <t>Mobiliario opción 5</t>
+  </si>
+  <si>
+    <t>Sergio Roldan</t>
   </si>
 </sst>
 </file>
@@ -287,7 +290,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -295,6 +298,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -629,7 +633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B70F061-023B-44EE-9E6E-8EEBF0F9DFA8}">
-  <dimension ref="A1:T27"/>
+  <dimension ref="A1:T28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
@@ -1621,6 +1625,56 @@
       <c r="S27" s="2"/>
       <c r="T27" s="2"/>
     </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28" s="2">
+        <v>1</v>
+      </c>
+      <c r="D28" s="2">
+        <v>1</v>
+      </c>
+      <c r="E28" s="2">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>1</v>
+      </c>
+      <c r="G28" s="2">
+        <v>1</v>
+      </c>
+      <c r="H28" s="2">
+        <v>1</v>
+      </c>
+      <c r="I28" s="2">
+        <v>1</v>
+      </c>
+      <c r="J28" s="7">
+        <v>1</v>
+      </c>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q28" s="2">
+        <v>1</v>
+      </c>
+      <c r="R28" s="2">
+        <v>1</v>
+      </c>
+      <c r="S28" s="2">
+        <v>1</v>
+      </c>
+      <c r="T28" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
